--- a/lab_1.xlsx
+++ b/lab_1.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Основне\Інститут\4 курс\1 семестр\Тестування\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{794B5647-71C8-491F-9D47-1C2283850F7E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C8E4E2F9-4DC7-4788-9E38-8D8954540431}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Аркуш1" sheetId="1" r:id="rId1"/>
@@ -64,18 +64,6 @@
     <t>Search by metadata playlist</t>
   </si>
   <si>
-    <t>See info about playlists</t>
-  </si>
-  <si>
-    <t>See personalized Home Page</t>
-  </si>
-  <si>
-    <t>See info About us</t>
-  </si>
-  <si>
-    <t>See info about Genre</t>
-  </si>
-  <si>
     <t>Features</t>
   </si>
   <si>
@@ -106,27 +94,12 @@
     <t>Log out</t>
   </si>
   <si>
-    <t>Apply filter for playlist by name</t>
-  </si>
-  <si>
-    <t>Apply filter for playlist by comment</t>
-  </si>
-  <si>
-    <t>See page Public Playlist</t>
-  </si>
-  <si>
     <t>Create comment</t>
   </si>
   <si>
     <t>View comments</t>
   </si>
   <si>
-    <t>See page My Playlist</t>
-  </si>
-  <si>
-    <t>Add playlist</t>
-  </si>
-  <si>
     <t>Edit playlist</t>
   </si>
   <si>
@@ -142,9 +115,6 @@
     <t>Share playlist</t>
   </si>
   <si>
-    <t>See page Share playlist</t>
-  </si>
-  <si>
     <t>Add like on song</t>
   </si>
   <si>
@@ -166,9 +136,6 @@
     <t>Search by friend</t>
   </si>
   <si>
-    <t>Email marketing</t>
-  </si>
-  <si>
     <t>Send email</t>
   </si>
   <si>
@@ -176,6 +143,39 @@
   </si>
   <si>
     <t>Recommendations</t>
+  </si>
+  <si>
+    <t>Form Public Playlists Page</t>
+  </si>
+  <si>
+    <t>Sorting playlist by name</t>
+  </si>
+  <si>
+    <t>Sorting playlist by comment</t>
+  </si>
+  <si>
+    <t>Implement personalized Home Page</t>
+  </si>
+  <si>
+    <t>Top songs of Genre</t>
+  </si>
+  <si>
+    <t>About us Page</t>
+  </si>
+  <si>
+    <t>My Playlist Page</t>
+  </si>
+  <si>
+    <t>Shared playlists Page</t>
+  </si>
+  <si>
+    <t>Playlist details Page</t>
+  </si>
+  <si>
+    <t>Create playlist</t>
+  </si>
+  <si>
+    <t>News letter subscription</t>
   </si>
 </sst>
 </file>
@@ -392,8 +392,8 @@
   <colors>
     <mruColors>
       <color rgb="FFF3A875"/>
+      <color rgb="FF94E9FA"/>
       <color rgb="FFE37FF7"/>
-      <color rgb="FF94E9FA"/>
     </mruColors>
   </colors>
   <extLst>
@@ -781,7 +781,7 @@
       </c>
       <c r="E1" s="4"/>
       <c r="F1" s="7" t="s">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="G1" s="1" t="s">
         <v>0</v>
@@ -798,7 +798,7 @@
         <v>1</v>
       </c>
       <c r="F2" s="18" t="s">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="G2" s="9" t="s">
         <v>2</v>
@@ -815,7 +815,7 @@
         <v>2</v>
       </c>
       <c r="F3" s="18" t="s">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="G3" s="9" t="s">
         <v>2</v>
@@ -826,13 +826,13 @@
         <v>3</v>
       </c>
       <c r="B4" s="13" t="s">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="E4" s="8">
         <v>3</v>
       </c>
       <c r="F4" s="18" t="s">
-        <v>21</v>
+        <v>17</v>
       </c>
       <c r="G4" s="9" t="s">
         <v>2</v>
@@ -843,7 +843,7 @@
         <v>4</v>
       </c>
       <c r="B5" s="33" t="s">
-        <v>45</v>
+        <v>34</v>
       </c>
       <c r="E5" s="8">
         <v>4</v>
@@ -860,7 +860,7 @@
         <v>5</v>
       </c>
       <c r="B6" s="30" t="s">
-        <v>44</v>
+        <v>33</v>
       </c>
       <c r="E6" s="8">
         <v>5</v>
@@ -877,7 +877,7 @@
         <v>6</v>
       </c>
       <c r="B7" s="26" t="s">
-        <v>17</v>
+        <v>13</v>
       </c>
       <c r="E7" s="8">
         <f t="shared" ref="E7:E19" si="0">E6+1</f>
@@ -895,14 +895,14 @@
         <v>7</v>
       </c>
       <c r="B8" s="15" t="s">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="E8" s="8">
         <f t="shared" si="0"/>
         <v>7</v>
       </c>
       <c r="F8" s="18" t="s">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="G8" s="9" t="s">
         <v>2</v>
@@ -913,29 +913,29 @@
         <v>8</v>
       </c>
       <c r="B9" s="17" t="s">
-        <v>42</v>
+        <v>45</v>
       </c>
       <c r="E9" s="8">
         <f t="shared" si="0"/>
         <v>8</v>
       </c>
       <c r="F9" s="18" t="s">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="G9" s="9" t="s">
         <v>2</v>
       </c>
     </row>
     <row r="10" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="E10" s="10">
+      <c r="E10" s="27">
         <f t="shared" si="0"/>
         <v>9</v>
       </c>
-      <c r="F10" s="19" t="s">
-        <v>24</v>
-      </c>
-      <c r="G10" s="11" t="s">
-        <v>1</v>
+      <c r="F10" s="28" t="s">
+        <v>35</v>
+      </c>
+      <c r="G10" s="26" t="s">
+        <v>13</v>
       </c>
     </row>
     <row r="11" spans="1:7" x14ac:dyDescent="0.3">
@@ -968,7 +968,7 @@
         <v>12</v>
       </c>
       <c r="F13" s="19" t="s">
-        <v>22</v>
+        <v>36</v>
       </c>
       <c r="G13" s="11" t="s">
         <v>1</v>
@@ -980,7 +980,7 @@
         <v>13</v>
       </c>
       <c r="F14" s="19" t="s">
-        <v>23</v>
+        <v>37</v>
       </c>
       <c r="G14" s="11" t="s">
         <v>1</v>
@@ -992,10 +992,10 @@
         <v>14</v>
       </c>
       <c r="F15" s="20" t="s">
-        <v>35</v>
+        <v>25</v>
       </c>
       <c r="G15" s="13" t="s">
-        <v>16</v>
+        <v>12</v>
       </c>
     </row>
     <row r="16" spans="1:7" x14ac:dyDescent="0.3">
@@ -1004,10 +1004,10 @@
         <v>15</v>
       </c>
       <c r="F16" s="20" t="s">
-        <v>36</v>
+        <v>26</v>
       </c>
       <c r="G16" s="13" t="s">
-        <v>16</v>
+        <v>12</v>
       </c>
     </row>
     <row r="17" spans="5:7" x14ac:dyDescent="0.3">
@@ -1016,10 +1016,10 @@
         <v>16</v>
       </c>
       <c r="F17" s="34" t="s">
-        <v>9</v>
+        <v>38</v>
       </c>
       <c r="G17" s="33" t="s">
-        <v>45</v>
+        <v>34</v>
       </c>
     </row>
     <row r="18" spans="5:7" x14ac:dyDescent="0.3">
@@ -1028,10 +1028,10 @@
         <v>17</v>
       </c>
       <c r="F18" s="34" t="s">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="G18" s="33" t="s">
-        <v>45</v>
+        <v>34</v>
       </c>
     </row>
     <row r="19" spans="5:7" x14ac:dyDescent="0.3">
@@ -1040,10 +1040,10 @@
         <v>18</v>
       </c>
       <c r="F19" s="34" t="s">
-        <v>11</v>
+        <v>39</v>
       </c>
       <c r="G19" s="35" t="s">
-        <v>45</v>
+        <v>34</v>
       </c>
     </row>
     <row r="20" spans="5:7" x14ac:dyDescent="0.3">
@@ -1052,10 +1052,10 @@
         <v>19</v>
       </c>
       <c r="F20" s="31" t="s">
-        <v>10</v>
+        <v>40</v>
       </c>
       <c r="G20" s="30" t="s">
-        <v>44</v>
+        <v>33</v>
       </c>
     </row>
     <row r="21" spans="5:7" x14ac:dyDescent="0.3">
@@ -1064,10 +1064,10 @@
         <v>20</v>
       </c>
       <c r="F21" s="28" t="s">
-        <v>8</v>
+        <v>43</v>
       </c>
       <c r="G21" s="26" t="s">
-        <v>17</v>
+        <v>13</v>
       </c>
     </row>
     <row r="22" spans="5:7" x14ac:dyDescent="0.3">
@@ -1076,10 +1076,10 @@
         <v>21</v>
       </c>
       <c r="F22" s="28" t="s">
-        <v>27</v>
+        <v>42</v>
       </c>
       <c r="G22" s="26" t="s">
-        <v>17</v>
+        <v>13</v>
       </c>
     </row>
     <row r="23" spans="5:7" x14ac:dyDescent="0.3">
@@ -1088,10 +1088,10 @@
         <v>22</v>
       </c>
       <c r="F23" s="28" t="s">
-        <v>28</v>
+        <v>41</v>
       </c>
       <c r="G23" s="26" t="s">
-        <v>17</v>
+        <v>13</v>
       </c>
     </row>
     <row r="24" spans="5:7" x14ac:dyDescent="0.3">
@@ -1100,10 +1100,10 @@
         <v>23</v>
       </c>
       <c r="F24" s="28" t="s">
-        <v>29</v>
+        <v>44</v>
       </c>
       <c r="G24" s="26" t="s">
-        <v>17</v>
+        <v>13</v>
       </c>
     </row>
     <row r="25" spans="5:7" x14ac:dyDescent="0.3">
@@ -1112,10 +1112,10 @@
         <v>24</v>
       </c>
       <c r="F25" s="28" t="s">
-        <v>30</v>
+        <v>20</v>
       </c>
       <c r="G25" s="26" t="s">
-        <v>17</v>
+        <v>13</v>
       </c>
     </row>
     <row r="26" spans="5:7" x14ac:dyDescent="0.3">
@@ -1124,10 +1124,10 @@
         <v>25</v>
       </c>
       <c r="F26" s="28" t="s">
-        <v>31</v>
+        <v>21</v>
       </c>
       <c r="G26" s="26" t="s">
-        <v>17</v>
+        <v>13</v>
       </c>
     </row>
     <row r="27" spans="5:7" x14ac:dyDescent="0.3">
@@ -1136,22 +1136,22 @@
         <v>26</v>
       </c>
       <c r="F27" s="28" t="s">
-        <v>32</v>
+        <v>22</v>
       </c>
       <c r="G27" s="26" t="s">
-        <v>17</v>
+        <v>13</v>
       </c>
     </row>
     <row r="28" spans="5:7" x14ac:dyDescent="0.3">
-      <c r="E28" s="21">
+      <c r="E28" s="27">
         <f t="shared" si="1"/>
         <v>27</v>
       </c>
-      <c r="F28" s="22" t="s">
-        <v>25</v>
-      </c>
-      <c r="G28" s="15" t="s">
-        <v>20</v>
+      <c r="F28" s="28" t="s">
+        <v>23</v>
+      </c>
+      <c r="G28" s="26" t="s">
+        <v>13</v>
       </c>
     </row>
     <row r="29" spans="5:7" x14ac:dyDescent="0.3">
@@ -1160,10 +1160,10 @@
         <v>28</v>
       </c>
       <c r="F29" s="22" t="s">
-        <v>26</v>
+        <v>18</v>
       </c>
       <c r="G29" s="15" t="s">
-        <v>20</v>
+        <v>16</v>
       </c>
     </row>
     <row r="30" spans="5:7" x14ac:dyDescent="0.3">
@@ -1172,10 +1172,10 @@
         <v>29</v>
       </c>
       <c r="F30" s="22" t="s">
-        <v>33</v>
+        <v>19</v>
       </c>
       <c r="G30" s="15" t="s">
-        <v>20</v>
+        <v>16</v>
       </c>
     </row>
     <row r="31" spans="5:7" x14ac:dyDescent="0.3">
@@ -1184,10 +1184,10 @@
         <v>30</v>
       </c>
       <c r="F31" s="22" t="s">
-        <v>34</v>
+        <v>24</v>
       </c>
       <c r="G31" s="15" t="s">
-        <v>20</v>
+        <v>16</v>
       </c>
     </row>
     <row r="32" spans="5:7" x14ac:dyDescent="0.3">
@@ -1196,10 +1196,10 @@
         <v>31</v>
       </c>
       <c r="F32" s="22" t="s">
-        <v>37</v>
+        <v>27</v>
       </c>
       <c r="G32" s="15" t="s">
-        <v>20</v>
+        <v>16</v>
       </c>
     </row>
     <row r="33" spans="5:7" x14ac:dyDescent="0.3">
@@ -1208,10 +1208,10 @@
         <v>32</v>
       </c>
       <c r="F33" s="22" t="s">
-        <v>38</v>
+        <v>28</v>
       </c>
       <c r="G33" s="15" t="s">
-        <v>20</v>
+        <v>16</v>
       </c>
     </row>
     <row r="34" spans="5:7" x14ac:dyDescent="0.3">
@@ -1220,10 +1220,10 @@
         <v>33</v>
       </c>
       <c r="F34" s="22" t="s">
-        <v>39</v>
+        <v>29</v>
       </c>
       <c r="G34" s="15" t="s">
-        <v>20</v>
+        <v>16</v>
       </c>
     </row>
     <row r="35" spans="5:7" x14ac:dyDescent="0.3">
@@ -1232,10 +1232,10 @@
         <v>34</v>
       </c>
       <c r="F35" s="22" t="s">
-        <v>40</v>
+        <v>30</v>
       </c>
       <c r="G35" s="15" t="s">
-        <v>20</v>
+        <v>16</v>
       </c>
     </row>
     <row r="36" spans="5:7" x14ac:dyDescent="0.3">
@@ -1244,10 +1244,10 @@
         <v>35</v>
       </c>
       <c r="F36" s="22" t="s">
-        <v>41</v>
+        <v>31</v>
       </c>
       <c r="G36" s="15" t="s">
-        <v>20</v>
+        <v>16</v>
       </c>
     </row>
     <row r="37" spans="5:7" x14ac:dyDescent="0.3">
@@ -1256,10 +1256,10 @@
         <v>36</v>
       </c>
       <c r="F37" s="24" t="s">
-        <v>43</v>
+        <v>32</v>
       </c>
       <c r="G37" s="17" t="s">
-        <v>42</v>
+        <v>45</v>
       </c>
     </row>
   </sheetData>
